--- a/data/gravel/Chiru Alpin 2025.xlsx
+++ b/data/gravel/Chiru Alpin 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4ADD93-EB9F-CC4C-A090-F40DA102F32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B1F935-5520-7B46-AADB-970276BED31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34600" yWindow="-20720" windowWidth="26260" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10820" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -317,13 +317,16 @@
   </si>
   <si>
     <t>frame only</t>
+  </si>
+  <si>
+    <t>https://www.chirubikes.com/wp-content/uploads/2023/06/chiru-alpin-gravel-cover-2.webp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -332,6 +335,13 @@
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
       <name val="Futura"/>
       <family val="2"/>
     </font>
@@ -353,15 +363,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -702,6 +715,11 @@
         <v>95</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
@@ -1330,6 +1348,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{114518B9-09B3-AC40-A4BA-B65238EBBD43}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/gravel/Chiru Alpin 2025.xlsx
+++ b/data/gravel/Chiru Alpin 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B1F935-5520-7B46-AADB-970276BED31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4C1210-B837-774E-BBC4-E5763FA6F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10820" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>https://www.chirubikes.com/wp-content/uploads/2023/06/chiru-alpin-gravel-cover-2.webp</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Paris, France</t>
   </si>
 </sst>
 </file>
@@ -669,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1347,6 +1353,14 @@
         <v>91</v>
       </c>
     </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{114518B9-09B3-AC40-A4BA-B65238EBBD43}"/>

--- a/data/gravel/Chiru Alpin 2025.xlsx
+++ b/data/gravel/Chiru Alpin 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4C1210-B837-774E-BBC4-E5763FA6F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D4EAF8-22E2-2A4E-9FAB-3CFC5ADE6B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -326,6 +326,24 @@
   </si>
   <si>
     <t>Paris, France</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -675,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1178,186 +1196,216 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49">
-        <v>27.2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51">
-        <v>44</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>64</v>
-      </c>
-      <c r="B52">
-        <v>48</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B55">
+        <v>27.2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
+      </c>
+      <c r="B57">
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>70</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>64</v>
+      </c>
+      <c r="B58">
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>78</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B67">
-        <v>2710</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73">
+        <v>2710</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>100</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B77" t="s">
         <v>101</v>
       </c>
     </row>

--- a/data/gravel/Chiru Alpin 2025.xlsx
+++ b/data/gravel/Chiru Alpin 2025.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D4EAF8-22E2-2A4E-9FAB-3CFC5ADE6B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203E3A82-A71D-6948-981B-3ED011538650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30120" yWindow="-17500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -344,6 +357,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>layback</t>
+  </si>
+  <si>
+    <t>eff SA angle</t>
+  </si>
+  <si>
+    <t>layback 1</t>
+  </si>
+  <si>
+    <t>this may be actual sta</t>
+  </si>
+  <si>
+    <t>tan(sta) = seat_v/seat_h</t>
   </si>
 </sst>
 </file>
@@ -693,13 +721,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -715,7 +743,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -723,7 +751,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -731,7 +759,7 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -739,12 +767,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -752,7 +780,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -769,7 +797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -785,8 +813,23 @@
       <c r="E9">
         <v>600</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9">
+        <f>C19/TAN(C15*PI()/180)</f>
+        <v>159.73893737846703</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:I9" si="0">D19/TAN(D15*PI()/180)</f>
+        <v>162.78950736312524</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>175.18735841223094</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -802,8 +845,23 @@
       <c r="E10">
         <v>475</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10">
+        <f>C9-C20</f>
+        <v>144</v>
+      </c>
+      <c r="H10">
+        <f t="shared" ref="H10:I10" si="1">D9-D20</f>
+        <v>144</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>156.19999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -819,8 +877,26 @@
       <c r="E11">
         <v>435</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11">
+        <f>ATAN(C19/G10)*180/PI()</f>
+        <v>75.963756532073532</v>
+      </c>
+      <c r="H11">
+        <f t="shared" ref="H11:I11" si="2">ATAN(D19/H10)*180/PI()</f>
+        <v>76.216665633718605</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>75.749133791843306</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -836,8 +912,10 @@
       <c r="E12">
         <v>1145</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -854,7 +932,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -871,8 +949,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B15" t="s">
@@ -887,8 +965,11 @@
       <c r="E15">
         <v>74.099999999999994</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
